--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -68736,7 +68736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69444,6 +69444,68 @@
         <v>6400995</v>
       </c>
       <c r="Z10" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5800800</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BTCUSD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>45906.61646990741</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>110787.3</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2025-09-06 14:48:19</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>110803.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>6428448</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
@@ -69524,19 +69586,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>16.02</v>
+        <v>16.18</v>
       </c>
       <c r="D3" t="n">
         <v>-519</v>
       </c>
       <c r="E3" t="n">
-        <v>-502.98</v>
+        <v>-502.82</v>
       </c>
       <c r="F3" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4504"/>
+  <dimension ref="A1:C4508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68725,6 +68725,74 @@
         </is>
       </c>
     </row>
+    <row r="4505">
+      <c r="A4505" t="inlineStr">
+        <is>
+          <t>2025-09-06 18:32:29</t>
+        </is>
+      </c>
+      <c r="B4505" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4505" t="inlineStr">
+        <is>
+          <t>Order send failed, retcode=10019, comment=No money</t>
+        </is>
+      </c>
+    </row>
+    <row r="4506">
+      <c r="A4506" t="inlineStr">
+        <is>
+          <t>2025-09-06 20:40:28</t>
+        </is>
+      </c>
+      <c r="B4506" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4506" t="inlineStr">
+        <is>
+          <t>Order send failed, retcode=10019, comment=No money</t>
+        </is>
+      </c>
+    </row>
+    <row r="4507">
+      <c r="A4507" t="inlineStr">
+        <is>
+          <t>2025-09-06 21:01:19</t>
+        </is>
+      </c>
+      <c r="B4507" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4507" t="inlineStr">
+        <is>
+          <t>Order send failed, retcode=10019, comment=No money</t>
+        </is>
+      </c>
+    </row>
+    <row r="4508">
+      <c r="A4508" t="inlineStr">
+        <is>
+          <t>2025-09-08 12:40:44</t>
+        </is>
+      </c>
+      <c r="B4508" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4508" t="inlineStr">
+        <is>
+          <t>Failed to modify SL/TP for ticket #5806473, retcode=10036, comment=Position doesn't exist</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4508"/>
+  <dimension ref="A1:C4515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68793,6 +68793,162 @@
         </is>
       </c>
     </row>
+    <row r="4509">
+      <c r="A4509" t="inlineStr">
+        <is>
+          <t>2025-09-08 23:20:20</t>
+        </is>
+      </c>
+      <c r="B4509" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4509" t="inlineStr">
+        <is>
+          <t>An unexpected error occurred in the main loop: cannot access local variable 'take_profit' where it is not associated with a value
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 148, in main_loop
+    sync_positions_with_state(tm)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 52, in sync_positions_with_state
+    adopt_manual_trade(tm, pos)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 73, in adopt_manual_trade
+    take_profit = price + tp_distance if trade_type == 'BUY' else price - take_profit
+                                                                          ^^^^^^^^^^^
+UnboundLocalError: cannot access local variable 'take_profit' where it is not associated with a value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4510">
+      <c r="A4510" t="inlineStr">
+        <is>
+          <t>2025-09-08 23:20:53</t>
+        </is>
+      </c>
+      <c r="B4510" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4510" t="inlineStr">
+        <is>
+          <t>An unexpected error occurred in the main loop: cannot access local variable 'take_profit' where it is not associated with a value
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 148, in main_loop
+    sync_positions_with_state(tm)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 52, in sync_positions_with_state
+    adopt_manual_trade(tm, pos)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 73, in adopt_manual_trade
+    take_profit = price + tp_distance if trade_type == 'BUY' else price - take_profit
+                                                                          ^^^^^^^^^^^
+UnboundLocalError: cannot access local variable 'take_profit' where it is not associated with a value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4511">
+      <c r="A4511" t="inlineStr">
+        <is>
+          <t>2025-09-08 23:21:26</t>
+        </is>
+      </c>
+      <c r="B4511" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4511" t="inlineStr">
+        <is>
+          <t>An unexpected error occurred in the main loop: cannot access local variable 'take_profit' where it is not associated with a value
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 148, in main_loop
+    sync_positions_with_state(tm)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 52, in sync_positions_with_state
+    adopt_manual_trade(tm, pos)
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 73, in adopt_manual_trade
+    take_profit = price + tp_distance if trade_type == 'BUY' else price - take_profit
+                                                                          ^^^^^^^^^^^
+UnboundLocalError: cannot access local variable 'take_profit' where it is not associated with a value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4512">
+      <c r="A4512" t="inlineStr">
+        <is>
+          <t>2025-09-09 19:02:58</t>
+        </is>
+      </c>
+      <c r="B4512" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4512" t="inlineStr">
+        <is>
+          <t>Failed to modify SL/TP for ticket #5849169, retcode=10036, comment=Position doesn't exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4513">
+      <c r="A4513" t="inlineStr">
+        <is>
+          <t>2025-09-10 19:04:28</t>
+        </is>
+      </c>
+      <c r="B4513" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4513" t="inlineStr">
+        <is>
+          <t>Order send failed, retcode=10016, comment=Invalid stops</t>
+        </is>
+      </c>
+    </row>
+    <row r="4514">
+      <c r="A4514" t="inlineStr">
+        <is>
+          <t>2025-09-10 20:54:07</t>
+        </is>
+      </c>
+      <c r="B4514" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C4514" t="inlineStr">
+        <is>
+          <t>Order send failed, retcode=10016, comment=Invalid stops</t>
+        </is>
+      </c>
+    </row>
+    <row r="4515">
+      <c r="A4515" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:27:06</t>
+        </is>
+      </c>
+      <c r="B4515" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4515" t="inlineStr">
+        <is>
+          <t>An unexpected error occurred in the main loop: module 'configs' has no attribute 'MIN_SEPARATION_PIPS'
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\main.py", line 152, in main_loop
+    strategy.check_and_execute()
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\strategy.py", line 72, in check_and_execute
+    df_entry = ind.calculate_ema_crossover_signal(
+               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\indicators.py", line 68, in calculate_ema_crossover_signal
+    min_separation_in_price = config.MIN_SEPARATION_PIPS * config.POINTS_PER_PIP * point
+                              ^^^^^^^^^^^^^^^^^^^^^^^^^^
+AttributeError: module 'configs' has no attribute 'MIN_SEPARATION_PIPS'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -68804,7 +68960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69574,6 +69730,68 @@
         <v>6428448</v>
       </c>
       <c r="Z11" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5829583</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>XAUUSD.d</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>45908.87096064815</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3634.46</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2025-09-08 20:54:58</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>3634.46</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>6457341</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
@@ -69654,7 +69872,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>16.18</v>
@@ -69666,7 +69884,7 @@
         <v>-502.82</v>
       </c>
       <c r="F3" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
     </row>
   </sheetData>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ActivityLog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TradeHistory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MonthlySummary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivityLog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TradeHistory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlySummary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4515"/>
+  <dimension ref="A1:C4523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68949,6 +68949,146 @@
         </is>
       </c>
     </row>
+    <row r="4516">
+      <c r="A4516" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:42:01</t>
+        </is>
+      </c>
+      <c r="B4516" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4516" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4517">
+      <c r="A4517" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:42:02</t>
+        </is>
+      </c>
+      <c r="B4517" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4517" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "E:\Cloned Github Repo\GoldieBot\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4518">
+      <c r="A4518" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:42:03</t>
+        </is>
+      </c>
+      <c r="B4518" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4518" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5. Shutting down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4519">
+      <c r="A4519" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:44:55</t>
+        </is>
+      </c>
+      <c r="B4519" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4519" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4520">
+      <c r="A4520" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:44:56</t>
+        </is>
+      </c>
+      <c r="B4520" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4520" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4521">
+      <c r="A4521" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:44:57</t>
+        </is>
+      </c>
+      <c r="B4521" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4521" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4522">
+      <c r="A4522" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:44:58</t>
+        </is>
+      </c>
+      <c r="B4522" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4522" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4523">
+      <c r="A4523" t="inlineStr">
+        <is>
+          <t>2025-09-11 11:45:04</t>
+        </is>
+      </c>
+      <c r="B4523" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4523" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivityLog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TradeHistory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlySummary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ActivityLog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TradeHistory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MonthlySummary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4523"/>
+  <dimension ref="A1:C4561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69089,6 +69089,656 @@
         </is>
       </c>
     </row>
+    <row r="4524">
+      <c r="A4524" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:06</t>
+        </is>
+      </c>
+      <c r="B4524" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4524" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4525">
+      <c r="A4525" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:08</t>
+        </is>
+      </c>
+      <c r="B4525" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4525" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4526">
+      <c r="A4526" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:09</t>
+        </is>
+      </c>
+      <c r="B4526" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4526" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5. Shutting down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4527">
+      <c r="A4527" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:14</t>
+        </is>
+      </c>
+      <c r="B4527" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4527" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4528">
+      <c r="A4528" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:15</t>
+        </is>
+      </c>
+      <c r="B4528" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4528" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4529">
+      <c r="A4529" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:16</t>
+        </is>
+      </c>
+      <c r="B4529" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4529" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4530">
+      <c r="A4530" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:17</t>
+        </is>
+      </c>
+      <c r="B4530" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4530" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4531">
+      <c r="A4531" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:23</t>
+        </is>
+      </c>
+      <c r="B4531" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4531" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4532">
+      <c r="A4532" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:24</t>
+        </is>
+      </c>
+      <c r="B4532" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4532" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4533">
+      <c r="A4533" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:25</t>
+        </is>
+      </c>
+      <c r="B4533" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4533" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4534">
+      <c r="A4534" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:27</t>
+        </is>
+      </c>
+      <c r="B4534" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4534" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4535">
+      <c r="A4535" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:41:33</t>
+        </is>
+      </c>
+      <c r="B4535" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4535" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4536">
+      <c r="A4536" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:27</t>
+        </is>
+      </c>
+      <c r="B4536" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4536" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4537">
+      <c r="A4537" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:28</t>
+        </is>
+      </c>
+      <c r="B4537" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4537" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4538">
+      <c r="A4538" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:29</t>
+        </is>
+      </c>
+      <c r="B4538" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4538" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4539">
+      <c r="A4539" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:30</t>
+        </is>
+      </c>
+      <c r="B4539" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4539" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4540">
+      <c r="A4540" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:36</t>
+        </is>
+      </c>
+      <c r="B4540" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4540" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4541">
+      <c r="A4541" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:37</t>
+        </is>
+      </c>
+      <c r="B4541" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4541" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4542">
+      <c r="A4542" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:38</t>
+        </is>
+      </c>
+      <c r="B4542" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4542" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4543">
+      <c r="A4543" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:39</t>
+        </is>
+      </c>
+      <c r="B4543" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4543" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4544">
+      <c r="A4544" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:45</t>
+        </is>
+      </c>
+      <c r="B4544" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4544" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4545">
+      <c r="A4545" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:46</t>
+        </is>
+      </c>
+      <c r="B4545" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4545" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4546">
+      <c r="A4546" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:48</t>
+        </is>
+      </c>
+      <c r="B4546" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4546" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4547">
+      <c r="A4547" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:49</t>
+        </is>
+      </c>
+      <c r="B4547" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4547" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4548">
+      <c r="A4548" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:55</t>
+        </is>
+      </c>
+      <c r="B4548" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4548" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4549">
+      <c r="A4549" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:56</t>
+        </is>
+      </c>
+      <c r="B4549" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4549" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4550">
+      <c r="A4550" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:57</t>
+        </is>
+      </c>
+      <c r="B4550" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4550" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4551">
+      <c r="A4551" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:43:58</t>
+        </is>
+      </c>
+      <c r="B4551" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4551" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4552">
+      <c r="A4552" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:04</t>
+        </is>
+      </c>
+      <c r="B4552" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4552" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4553">
+      <c r="A4553" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:05</t>
+        </is>
+      </c>
+      <c r="B4553" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4553" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4554">
+      <c r="A4554" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:07</t>
+        </is>
+      </c>
+      <c r="B4554" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4554" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4555">
+      <c r="A4555" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:08</t>
+        </is>
+      </c>
+      <c r="B4555" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4555" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4556">
+      <c r="A4556" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:14</t>
+        </is>
+      </c>
+      <c r="B4556" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4556" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4557">
+      <c r="A4557" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:15</t>
+        </is>
+      </c>
+      <c r="B4557" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4557" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4558">
+      <c r="A4558" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:16</t>
+        </is>
+      </c>
+      <c r="B4558" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4558" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4559">
+      <c r="A4559" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:17</t>
+        </is>
+      </c>
+      <c r="B4559" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4559" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4560">
+      <c r="A4560" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:23</t>
+        </is>
+      </c>
+      <c r="B4560" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4560" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4561">
+      <c r="A4561" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:25</t>
+        </is>
+      </c>
+      <c r="B4561" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4561" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4561"/>
+  <dimension ref="A1:C4686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69739,6 +69739,2131 @@
         </is>
       </c>
     </row>
+    <row r="4562">
+      <c r="A4562" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:26</t>
+        </is>
+      </c>
+      <c r="B4562" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4562" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4563">
+      <c r="A4563" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:28</t>
+        </is>
+      </c>
+      <c r="B4563" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4563" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4564">
+      <c r="A4564" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:34</t>
+        </is>
+      </c>
+      <c r="B4564" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4564" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4565">
+      <c r="A4565" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:36</t>
+        </is>
+      </c>
+      <c r="B4565" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4565" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4566">
+      <c r="A4566" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:37</t>
+        </is>
+      </c>
+      <c r="B4566" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4566" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4567">
+      <c r="A4567" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:38</t>
+        </is>
+      </c>
+      <c r="B4567" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4567" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4568">
+      <c r="A4568" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:45</t>
+        </is>
+      </c>
+      <c r="B4568" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4568" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4569">
+      <c r="A4569" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:46</t>
+        </is>
+      </c>
+      <c r="B4569" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4569" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4570">
+      <c r="A4570" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:47</t>
+        </is>
+      </c>
+      <c r="B4570" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4570" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4571">
+      <c r="A4571" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:48</t>
+        </is>
+      </c>
+      <c r="B4571" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4571" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4572">
+      <c r="A4572" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:55</t>
+        </is>
+      </c>
+      <c r="B4572" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4572" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4573">
+      <c r="A4573" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:56</t>
+        </is>
+      </c>
+      <c r="B4573" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4573" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4574">
+      <c r="A4574" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:58</t>
+        </is>
+      </c>
+      <c r="B4574" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4574" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4575">
+      <c r="A4575" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:44:59</t>
+        </is>
+      </c>
+      <c r="B4575" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4575" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4576">
+      <c r="A4576" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:05</t>
+        </is>
+      </c>
+      <c r="B4576" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4576" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4577">
+      <c r="A4577" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:07</t>
+        </is>
+      </c>
+      <c r="B4577" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4577" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4578">
+      <c r="A4578" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:08</t>
+        </is>
+      </c>
+      <c r="B4578" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4578" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4579">
+      <c r="A4579" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:10</t>
+        </is>
+      </c>
+      <c r="B4579" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4579" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4580">
+      <c r="A4580" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:16</t>
+        </is>
+      </c>
+      <c r="B4580" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4580" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4581">
+      <c r="A4581" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:18</t>
+        </is>
+      </c>
+      <c r="B4581" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4581" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4582">
+      <c r="A4582" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:19</t>
+        </is>
+      </c>
+      <c r="B4582" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4582" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4583">
+      <c r="A4583" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:21</t>
+        </is>
+      </c>
+      <c r="B4583" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4583" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:27</t>
+        </is>
+      </c>
+      <c r="B4584" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4584" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:28</t>
+        </is>
+      </c>
+      <c r="B4585" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4585" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:30</t>
+        </is>
+      </c>
+      <c r="B4586" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4586" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:31</t>
+        </is>
+      </c>
+      <c r="B4587" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4587" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:38</t>
+        </is>
+      </c>
+      <c r="B4588" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4588" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:39</t>
+        </is>
+      </c>
+      <c r="B4589" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4589" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:40</t>
+        </is>
+      </c>
+      <c r="B4590" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4590" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:42</t>
+        </is>
+      </c>
+      <c r="B4591" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4591" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:48</t>
+        </is>
+      </c>
+      <c r="B4592" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4592" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:50</t>
+        </is>
+      </c>
+      <c r="B4593" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4593" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:51</t>
+        </is>
+      </c>
+      <c r="B4594" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4594" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:52</t>
+        </is>
+      </c>
+      <c r="B4595" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4595" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:45:59</t>
+        </is>
+      </c>
+      <c r="B4596" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4596" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:00</t>
+        </is>
+      </c>
+      <c r="B4597" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4597" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:02</t>
+        </is>
+      </c>
+      <c r="B4598" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4598" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:03</t>
+        </is>
+      </c>
+      <c r="B4599" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4599" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:10</t>
+        </is>
+      </c>
+      <c r="B4600" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4600" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:11</t>
+        </is>
+      </c>
+      <c r="B4601" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4601" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:13</t>
+        </is>
+      </c>
+      <c r="B4602" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4602" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:14</t>
+        </is>
+      </c>
+      <c r="B4603" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4603" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:21</t>
+        </is>
+      </c>
+      <c r="B4604" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4604" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:23</t>
+        </is>
+      </c>
+      <c r="B4605" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4605" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:24</t>
+        </is>
+      </c>
+      <c r="B4606" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4606" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:26</t>
+        </is>
+      </c>
+      <c r="B4607" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4607" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:32</t>
+        </is>
+      </c>
+      <c r="B4608" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4608" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:33</t>
+        </is>
+      </c>
+      <c r="B4609" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4609" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:34</t>
+        </is>
+      </c>
+      <c r="B4610" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4610" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:36</t>
+        </is>
+      </c>
+      <c r="B4611" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4611" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:42</t>
+        </is>
+      </c>
+      <c r="B4612" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4612" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4613">
+      <c r="A4613" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:43</t>
+        </is>
+      </c>
+      <c r="B4613" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4613" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4614">
+      <c r="A4614" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:44</t>
+        </is>
+      </c>
+      <c r="B4614" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4614" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4615">
+      <c r="A4615" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:45</t>
+        </is>
+      </c>
+      <c r="B4615" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4615" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4616">
+      <c r="A4616" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:51</t>
+        </is>
+      </c>
+      <c r="B4616" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4616" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4617">
+      <c r="A4617" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:52</t>
+        </is>
+      </c>
+      <c r="B4617" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4617" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4618">
+      <c r="A4618" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:53</t>
+        </is>
+      </c>
+      <c r="B4618" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4618" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4619">
+      <c r="A4619" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:46:54</t>
+        </is>
+      </c>
+      <c r="B4619" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4619" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4620">
+      <c r="A4620" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:02</t>
+        </is>
+      </c>
+      <c r="B4620" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4620" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4621">
+      <c r="A4621" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:03</t>
+        </is>
+      </c>
+      <c r="B4621" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4621" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4622">
+      <c r="A4622" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:05</t>
+        </is>
+      </c>
+      <c r="B4622" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4622" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4623">
+      <c r="A4623" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:07</t>
+        </is>
+      </c>
+      <c r="B4623" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4623" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4624">
+      <c r="A4624" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:13</t>
+        </is>
+      </c>
+      <c r="B4624" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4624" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4625">
+      <c r="A4625" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:15</t>
+        </is>
+      </c>
+      <c r="B4625" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4625" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4626">
+      <c r="A4626" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:16</t>
+        </is>
+      </c>
+      <c r="B4626" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4626" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4627">
+      <c r="A4627" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:17</t>
+        </is>
+      </c>
+      <c r="B4627" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4627" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4628">
+      <c r="A4628" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:24</t>
+        </is>
+      </c>
+      <c r="B4628" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4628" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4629">
+      <c r="A4629" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:25</t>
+        </is>
+      </c>
+      <c r="B4629" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4629" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4630">
+      <c r="A4630" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:26</t>
+        </is>
+      </c>
+      <c r="B4630" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4630" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4631">
+      <c r="A4631" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:27</t>
+        </is>
+      </c>
+      <c r="B4631" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4631" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4632">
+      <c r="A4632" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:33</t>
+        </is>
+      </c>
+      <c r="B4632" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4632" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4633">
+      <c r="A4633" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:34</t>
+        </is>
+      </c>
+      <c r="B4633" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4633" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4634">
+      <c r="A4634" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:35</t>
+        </is>
+      </c>
+      <c r="B4634" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4634" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4635">
+      <c r="A4635" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:37</t>
+        </is>
+      </c>
+      <c r="B4635" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4635" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4636">
+      <c r="A4636" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:43</t>
+        </is>
+      </c>
+      <c r="B4636" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4636" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4637">
+      <c r="A4637" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:44</t>
+        </is>
+      </c>
+      <c r="B4637" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4637" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4638">
+      <c r="A4638" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:45</t>
+        </is>
+      </c>
+      <c r="B4638" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4638" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4639">
+      <c r="A4639" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:46</t>
+        </is>
+      </c>
+      <c r="B4639" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4639" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4640">
+      <c r="A4640" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:52</t>
+        </is>
+      </c>
+      <c r="B4640" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4640" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4641">
+      <c r="A4641" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:53</t>
+        </is>
+      </c>
+      <c r="B4641" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4641" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4642">
+      <c r="A4642" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:54</t>
+        </is>
+      </c>
+      <c r="B4642" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4642" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4643">
+      <c r="A4643" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:47:55</t>
+        </is>
+      </c>
+      <c r="B4643" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4643" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4644">
+      <c r="A4644" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:01</t>
+        </is>
+      </c>
+      <c r="B4644" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4644" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4645">
+      <c r="A4645" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:03</t>
+        </is>
+      </c>
+      <c r="B4645" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4645" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4646">
+      <c r="A4646" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:04</t>
+        </is>
+      </c>
+      <c r="B4646" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4646" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4647">
+      <c r="A4647" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:05</t>
+        </is>
+      </c>
+      <c r="B4647" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4647" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4648">
+      <c r="A4648" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:11</t>
+        </is>
+      </c>
+      <c r="B4648" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4648" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4649">
+      <c r="A4649" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:12</t>
+        </is>
+      </c>
+      <c r="B4649" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4649" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4650">
+      <c r="A4650" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:13</t>
+        </is>
+      </c>
+      <c r="B4650" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4650" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4651">
+      <c r="A4651" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:14</t>
+        </is>
+      </c>
+      <c r="B4651" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4651" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4652">
+      <c r="A4652" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:21</t>
+        </is>
+      </c>
+      <c r="B4652" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4652" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4653">
+      <c r="A4653" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:23</t>
+        </is>
+      </c>
+      <c r="B4653" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4653" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4654">
+      <c r="A4654" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:24</t>
+        </is>
+      </c>
+      <c r="B4654" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4654" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4655">
+      <c r="A4655" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:26</t>
+        </is>
+      </c>
+      <c r="B4655" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4655" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4656">
+      <c r="A4656" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:33</t>
+        </is>
+      </c>
+      <c r="B4656" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4656" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4657">
+      <c r="A4657" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:35</t>
+        </is>
+      </c>
+      <c r="B4657" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4657" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4658">
+      <c r="A4658" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:36</t>
+        </is>
+      </c>
+      <c r="B4658" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4658" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4659">
+      <c r="A4659" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:38</t>
+        </is>
+      </c>
+      <c r="B4659" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4659" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4660">
+      <c r="A4660" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:44</t>
+        </is>
+      </c>
+      <c r="B4660" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4660" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4661">
+      <c r="A4661" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:48</t>
+        </is>
+      </c>
+      <c r="B4661" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4661" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4662">
+      <c r="A4662" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:53</t>
+        </is>
+      </c>
+      <c r="B4662" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4662" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4663">
+      <c r="A4663" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:48:56</t>
+        </is>
+      </c>
+      <c r="B4663" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4663" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4664">
+      <c r="A4664" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:07</t>
+        </is>
+      </c>
+      <c r="B4664" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4664" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4665">
+      <c r="A4665" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:09</t>
+        </is>
+      </c>
+      <c r="B4665" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4665" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4666">
+      <c r="A4666" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:11</t>
+        </is>
+      </c>
+      <c r="B4666" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4666" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4667">
+      <c r="A4667" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:13</t>
+        </is>
+      </c>
+      <c r="B4667" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4667" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4668">
+      <c r="A4668" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:19</t>
+        </is>
+      </c>
+      <c r="B4668" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4668" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4669">
+      <c r="A4669" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:20</t>
+        </is>
+      </c>
+      <c r="B4669" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4669" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4670">
+      <c r="A4670" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:22</t>
+        </is>
+      </c>
+      <c r="B4670" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4670" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4671">
+      <c r="A4671" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:24</t>
+        </is>
+      </c>
+      <c r="B4671" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4671" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4672">
+      <c r="A4672" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:31</t>
+        </is>
+      </c>
+      <c r="B4672" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4672" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4673">
+      <c r="A4673" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:32</t>
+        </is>
+      </c>
+      <c r="B4673" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4673" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4674">
+      <c r="A4674" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:33</t>
+        </is>
+      </c>
+      <c r="B4674" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4674" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4675">
+      <c r="A4675" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:34</t>
+        </is>
+      </c>
+      <c r="B4675" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4675" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4676">
+      <c r="A4676" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:40</t>
+        </is>
+      </c>
+      <c r="B4676" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4676" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4677">
+      <c r="A4677" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:41</t>
+        </is>
+      </c>
+      <c r="B4677" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4677" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4678">
+      <c r="A4678" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:42</t>
+        </is>
+      </c>
+      <c r="B4678" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4678" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4679">
+      <c r="A4679" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:49</t>
+        </is>
+      </c>
+      <c r="B4679" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4679" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4680">
+      <c r="A4680" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:50</t>
+        </is>
+      </c>
+      <c r="B4680" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4680" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4681">
+      <c r="A4681" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:51</t>
+        </is>
+      </c>
+      <c r="B4681" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4681" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4682">
+      <c r="A4682" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:52</t>
+        </is>
+      </c>
+      <c r="B4682" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4682" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4683">
+      <c r="A4683" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:58</t>
+        </is>
+      </c>
+      <c r="B4683" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4683" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4684">
+      <c r="A4684" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:49:59</t>
+        </is>
+      </c>
+      <c r="B4684" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4684" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4685">
+      <c r="A4685" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:50:00</t>
+        </is>
+      </c>
+      <c r="B4685" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4685" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4686">
+      <c r="A4686" t="inlineStr">
+        <is>
+          <t>2025-09-11 12:50:02</t>
+        </is>
+      </c>
+      <c r="B4686" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4686" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4686"/>
+  <dimension ref="A1:C4726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71864,6 +71864,698 @@
         </is>
       </c>
     </row>
+    <row r="4687">
+      <c r="A4687" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:38</t>
+        </is>
+      </c>
+      <c r="B4687" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4687" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4688">
+      <c r="A4688" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:39</t>
+        </is>
+      </c>
+      <c r="B4688" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4688" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4689">
+      <c r="A4689" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:41</t>
+        </is>
+      </c>
+      <c r="B4689" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4689" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5. Shutting down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4690">
+      <c r="A4690" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:47</t>
+        </is>
+      </c>
+      <c r="B4690" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4690" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4691">
+      <c r="A4691" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:48</t>
+        </is>
+      </c>
+      <c r="B4691" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4691" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4692">
+      <c r="A4692" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:49</t>
+        </is>
+      </c>
+      <c r="B4692" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4692" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4693">
+      <c r="A4693" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:55</t>
+        </is>
+      </c>
+      <c r="B4693" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4693" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4694">
+      <c r="A4694" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:03:56</t>
+        </is>
+      </c>
+      <c r="B4694" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4694" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4695">
+      <c r="A4695" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:04:02</t>
+        </is>
+      </c>
+      <c r="B4695" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4695" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. Possible connection issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4696">
+      <c r="A4696" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:17</t>
+        </is>
+      </c>
+      <c r="B4696" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4696" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4697">
+      <c r="A4697" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:18</t>
+        </is>
+      </c>
+      <c r="B4697" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4697" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4698">
+      <c r="A4698" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:19</t>
+        </is>
+      </c>
+      <c r="B4698" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4698" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4699">
+      <c r="A4699" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:25</t>
+        </is>
+      </c>
+      <c r="B4699" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4699" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4700">
+      <c r="A4700" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:27</t>
+        </is>
+      </c>
+      <c r="B4700" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4700" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4701">
+      <c r="A4701" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:33</t>
+        </is>
+      </c>
+      <c r="B4701" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4701" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4702">
+      <c r="A4702" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:34</t>
+        </is>
+      </c>
+      <c r="B4702" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4702" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4703">
+      <c r="A4703" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:40</t>
+        </is>
+      </c>
+      <c r="B4703" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4703" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4704">
+      <c r="A4704" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:41</t>
+        </is>
+      </c>
+      <c r="B4704" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4704" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4705">
+      <c r="A4705" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:47</t>
+        </is>
+      </c>
+      <c r="B4705" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4705" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4706">
+      <c r="A4706" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:48</t>
+        </is>
+      </c>
+      <c r="B4706" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4706" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4707">
+      <c r="A4707" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:54</t>
+        </is>
+      </c>
+      <c r="B4707" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4707" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4708">
+      <c r="A4708" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:10:55</t>
+        </is>
+      </c>
+      <c r="B4708" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4708" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4709">
+      <c r="A4709" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:01</t>
+        </is>
+      </c>
+      <c r="B4709" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4709" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4710">
+      <c r="A4710" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:03</t>
+        </is>
+      </c>
+      <c r="B4710" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4710" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4711">
+      <c r="A4711" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:09</t>
+        </is>
+      </c>
+      <c r="B4711" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4711" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4712">
+      <c r="A4712" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:10</t>
+        </is>
+      </c>
+      <c r="B4712" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4712" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4713">
+      <c r="A4713" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:17</t>
+        </is>
+      </c>
+      <c r="B4713" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4713" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4714">
+      <c r="A4714" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:18</t>
+        </is>
+      </c>
+      <c r="B4714" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4714" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4715">
+      <c r="A4715" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:24</t>
+        </is>
+      </c>
+      <c r="B4715" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4715" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4716">
+      <c r="A4716" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:25</t>
+        </is>
+      </c>
+      <c r="B4716" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4716" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4717">
+      <c r="A4717" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:31</t>
+        </is>
+      </c>
+      <c r="B4717" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4717" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4718">
+      <c r="A4718" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:11:32</t>
+        </is>
+      </c>
+      <c r="B4718" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4718" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4719">
+      <c r="A4719" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:13:41</t>
+        </is>
+      </c>
+      <c r="B4719" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4719" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4720">
+      <c r="A4720" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:13:42</t>
+        </is>
+      </c>
+      <c r="B4720" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4720" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4721">
+      <c r="A4721" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:13:44</t>
+        </is>
+      </c>
+      <c r="B4721" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4721" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4722">
+      <c r="A4722" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:13:45</t>
+        </is>
+      </c>
+      <c r="B4722" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4722" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4723">
+      <c r="A4723" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:15:07</t>
+        </is>
+      </c>
+      <c r="B4723" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4723" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4724">
+      <c r="A4724" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:15:09</t>
+        </is>
+      </c>
+      <c r="B4724" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4724" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4725">
+      <c r="A4725" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:15:10</t>
+        </is>
+      </c>
+      <c r="B4725" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4725" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4726">
+      <c r="A4726" t="inlineStr">
+        <is>
+          <t>2025-09-11 13:15:11</t>
+        </is>
+      </c>
+      <c r="B4726" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4726" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4726"/>
+  <dimension ref="A1:C4805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72556,6 +72556,1357 @@
         </is>
       </c>
     </row>
+    <row r="4727">
+      <c r="A4727" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:26:35</t>
+        </is>
+      </c>
+      <c r="B4727" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4727" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4728">
+      <c r="A4728" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:26:38</t>
+        </is>
+      </c>
+      <c r="B4728" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4728" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4729">
+      <c r="A4729" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:26:40</t>
+        </is>
+      </c>
+      <c r="B4729" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4729" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4730">
+      <c r="A4730" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:26:41</t>
+        </is>
+      </c>
+      <c r="B4730" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4730" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4731">
+      <c r="A4731" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:21</t>
+        </is>
+      </c>
+      <c r="B4731" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4731" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4732">
+      <c r="A4732" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:23</t>
+        </is>
+      </c>
+      <c r="B4732" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4732" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4733">
+      <c r="A4733" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:24</t>
+        </is>
+      </c>
+      <c r="B4733" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4733" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4734">
+      <c r="A4734" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:25</t>
+        </is>
+      </c>
+      <c r="B4734" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4734" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4735">
+      <c r="A4735" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:44</t>
+        </is>
+      </c>
+      <c r="B4735" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4735" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4736">
+      <c r="A4736" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:45</t>
+        </is>
+      </c>
+      <c r="B4736" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4736" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4737">
+      <c r="A4737" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:46</t>
+        </is>
+      </c>
+      <c r="B4737" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4737" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4738">
+      <c r="A4738" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:53</t>
+        </is>
+      </c>
+      <c r="B4738" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4738" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4739">
+      <c r="A4739" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:30:54</t>
+        </is>
+      </c>
+      <c r="B4739" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4739" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4740">
+      <c r="A4740" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:00</t>
+        </is>
+      </c>
+      <c r="B4740" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4740" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4741">
+      <c r="A4741" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:02</t>
+        </is>
+      </c>
+      <c r="B4741" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4741" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4742">
+      <c r="A4742" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:08</t>
+        </is>
+      </c>
+      <c r="B4742" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4742" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4743">
+      <c r="A4743" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:10</t>
+        </is>
+      </c>
+      <c r="B4743" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4743" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4744">
+      <c r="A4744" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:16</t>
+        </is>
+      </c>
+      <c r="B4744" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4744" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4745">
+      <c r="A4745" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:17</t>
+        </is>
+      </c>
+      <c r="B4745" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4745" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4746">
+      <c r="A4746" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:23</t>
+        </is>
+      </c>
+      <c r="B4746" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4746" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4747">
+      <c r="A4747" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:24</t>
+        </is>
+      </c>
+      <c r="B4747" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4747" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4748">
+      <c r="A4748" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:31</t>
+        </is>
+      </c>
+      <c r="B4748" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4748" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4749">
+      <c r="A4749" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:32</t>
+        </is>
+      </c>
+      <c r="B4749" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4749" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4750">
+      <c r="A4750" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:38</t>
+        </is>
+      </c>
+      <c r="B4750" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4750" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4751">
+      <c r="A4751" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:39</t>
+        </is>
+      </c>
+      <c r="B4751" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4751" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4752">
+      <c r="A4752" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:46</t>
+        </is>
+      </c>
+      <c r="B4752" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4752" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4753">
+      <c r="A4753" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:47</t>
+        </is>
+      </c>
+      <c r="B4753" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4753" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4754">
+      <c r="A4754" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:53</t>
+        </is>
+      </c>
+      <c r="B4754" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4754" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4755">
+      <c r="A4755" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:31:54</t>
+        </is>
+      </c>
+      <c r="B4755" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4755" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4756">
+      <c r="A4756" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:00</t>
+        </is>
+      </c>
+      <c r="B4756" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4756" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4757">
+      <c r="A4757" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:01</t>
+        </is>
+      </c>
+      <c r="B4757" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4757" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4758">
+      <c r="A4758" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:08</t>
+        </is>
+      </c>
+      <c r="B4758" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4758" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4759">
+      <c r="A4759" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:09</t>
+        </is>
+      </c>
+      <c r="B4759" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4759" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4760">
+      <c r="A4760" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:15</t>
+        </is>
+      </c>
+      <c r="B4760" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4760" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4761">
+      <c r="A4761" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:16</t>
+        </is>
+      </c>
+      <c r="B4761" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4761" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4762">
+      <c r="A4762" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:23</t>
+        </is>
+      </c>
+      <c r="B4762" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4762" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4763">
+      <c r="A4763" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:24</t>
+        </is>
+      </c>
+      <c r="B4763" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4763" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4764">
+      <c r="A4764" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:30</t>
+        </is>
+      </c>
+      <c r="B4764" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4764" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4765">
+      <c r="A4765" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:31</t>
+        </is>
+      </c>
+      <c r="B4765" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4765" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4766">
+      <c r="A4766" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:37</t>
+        </is>
+      </c>
+      <c r="B4766" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4766" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4767">
+      <c r="A4767" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:38</t>
+        </is>
+      </c>
+      <c r="B4767" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4767" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4768">
+      <c r="A4768" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:45</t>
+        </is>
+      </c>
+      <c r="B4768" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4768" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4769">
+      <c r="A4769" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:46</t>
+        </is>
+      </c>
+      <c r="B4769" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4769" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4770">
+      <c r="A4770" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:52</t>
+        </is>
+      </c>
+      <c r="B4770" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4770" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4771">
+      <c r="A4771" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:32:53</t>
+        </is>
+      </c>
+      <c r="B4771" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4771" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:00</t>
+        </is>
+      </c>
+      <c r="B4772" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4772" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:01</t>
+        </is>
+      </c>
+      <c r="B4773" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4773" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:08</t>
+        </is>
+      </c>
+      <c r="B4774" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4774" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:09</t>
+        </is>
+      </c>
+      <c r="B4775" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4775" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4776">
+      <c r="A4776" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:15</t>
+        </is>
+      </c>
+      <c r="B4776" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4776" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4777">
+      <c r="A4777" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:16</t>
+        </is>
+      </c>
+      <c r="B4777" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4777" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4778">
+      <c r="A4778" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:22</t>
+        </is>
+      </c>
+      <c r="B4778" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4778" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:24</t>
+        </is>
+      </c>
+      <c r="B4779" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4779" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:30</t>
+        </is>
+      </c>
+      <c r="B4780" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4780" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4781">
+      <c r="A4781" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:31</t>
+        </is>
+      </c>
+      <c r="B4781" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4781" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:37</t>
+        </is>
+      </c>
+      <c r="B4782" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4782" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4783">
+      <c r="A4783" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:38</t>
+        </is>
+      </c>
+      <c r="B4783" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4783" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4784">
+      <c r="A4784" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:44</t>
+        </is>
+      </c>
+      <c r="B4784" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4784" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4785">
+      <c r="A4785" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:45</t>
+        </is>
+      </c>
+      <c r="B4785" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4785" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:51</t>
+        </is>
+      </c>
+      <c r="B4786" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4786" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:52</t>
+        </is>
+      </c>
+      <c r="B4787" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4787" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:33:58</t>
+        </is>
+      </c>
+      <c r="B4788" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4788" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4789">
+      <c r="A4789" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:00</t>
+        </is>
+      </c>
+      <c r="B4789" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4789" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4790">
+      <c r="A4790" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:06</t>
+        </is>
+      </c>
+      <c r="B4790" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4790" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:07</t>
+        </is>
+      </c>
+      <c r="B4791" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4791" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:13</t>
+        </is>
+      </c>
+      <c r="B4792" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4792" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4793">
+      <c r="A4793" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:14</t>
+        </is>
+      </c>
+      <c r="B4793" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4793" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4794">
+      <c r="A4794" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:21</t>
+        </is>
+      </c>
+      <c r="B4794" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4794" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4795">
+      <c r="A4795" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:22</t>
+        </is>
+      </c>
+      <c r="B4795" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4795" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4796">
+      <c r="A4796" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:28</t>
+        </is>
+      </c>
+      <c r="B4796" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4796" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4797">
+      <c r="A4797" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:29</t>
+        </is>
+      </c>
+      <c r="B4797" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4797" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4798">
+      <c r="A4798" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:35</t>
+        </is>
+      </c>
+      <c r="B4798" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4798" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4799">
+      <c r="A4799" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:36</t>
+        </is>
+      </c>
+      <c r="B4799" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4799" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:42</t>
+        </is>
+      </c>
+      <c r="B4800" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4800" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:44</t>
+        </is>
+      </c>
+      <c r="B4801" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4801" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4802">
+      <c r="A4802" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:50</t>
+        </is>
+      </c>
+      <c r="B4802" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4802" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:52</t>
+        </is>
+      </c>
+      <c r="B4803" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4803" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4804">
+      <c r="A4804" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:34:59</t>
+        </is>
+      </c>
+      <c r="B4804" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4804" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4805">
+      <c r="A4805" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:00</t>
+        </is>
+      </c>
+      <c r="B4805" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4805" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/trading_report.xlsx
+++ b/logs/trading_report.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4805"/>
+  <dimension ref="A1:C5319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73907,6 +73907,8748 @@
         </is>
       </c>
     </row>
+    <row r="4806">
+      <c r="A4806" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:07</t>
+        </is>
+      </c>
+      <c r="B4806" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4806" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:09</t>
+        </is>
+      </c>
+      <c r="B4807" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4807" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4808">
+      <c r="A4808" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:15</t>
+        </is>
+      </c>
+      <c r="B4808" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4808" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:16</t>
+        </is>
+      </c>
+      <c r="B4809" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4809" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:23</t>
+        </is>
+      </c>
+      <c r="B4810" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4810" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:24</t>
+        </is>
+      </c>
+      <c r="B4811" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4811" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:30</t>
+        </is>
+      </c>
+      <c r="B4812" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4812" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4813">
+      <c r="A4813" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:31</t>
+        </is>
+      </c>
+      <c r="B4813" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4813" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:37</t>
+        </is>
+      </c>
+      <c r="B4814" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4814" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4815">
+      <c r="A4815" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:39</t>
+        </is>
+      </c>
+      <c r="B4815" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4815" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:45</t>
+        </is>
+      </c>
+      <c r="B4816" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4816" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:46</t>
+        </is>
+      </c>
+      <c r="B4817" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4817" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4818">
+      <c r="A4818" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:52</t>
+        </is>
+      </c>
+      <c r="B4818" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4818" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4819">
+      <c r="A4819" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:53</t>
+        </is>
+      </c>
+      <c r="B4819" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4819" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:35:59</t>
+        </is>
+      </c>
+      <c r="B4820" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4820" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:01</t>
+        </is>
+      </c>
+      <c r="B4821" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4821" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4822">
+      <c r="A4822" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:07</t>
+        </is>
+      </c>
+      <c r="B4822" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4822" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:08</t>
+        </is>
+      </c>
+      <c r="B4823" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4823" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:15</t>
+        </is>
+      </c>
+      <c r="B4824" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4824" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:16</t>
+        </is>
+      </c>
+      <c r="B4825" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4825" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4826">
+      <c r="A4826" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:22</t>
+        </is>
+      </c>
+      <c r="B4826" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4826" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4827">
+      <c r="A4827" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:23</t>
+        </is>
+      </c>
+      <c r="B4827" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4827" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4828">
+      <c r="A4828" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:29</t>
+        </is>
+      </c>
+      <c r="B4828" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4828" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4829">
+      <c r="A4829" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:30</t>
+        </is>
+      </c>
+      <c r="B4829" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4829" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4830">
+      <c r="A4830" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:36</t>
+        </is>
+      </c>
+      <c r="B4830" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4830" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4831">
+      <c r="A4831" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:38</t>
+        </is>
+      </c>
+      <c r="B4831" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4831" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4832">
+      <c r="A4832" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:44</t>
+        </is>
+      </c>
+      <c r="B4832" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4832" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4833">
+      <c r="A4833" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:45</t>
+        </is>
+      </c>
+      <c r="B4833" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4833" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4834">
+      <c r="A4834" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:51</t>
+        </is>
+      </c>
+      <c r="B4834" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4834" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4835">
+      <c r="A4835" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:52</t>
+        </is>
+      </c>
+      <c r="B4835" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4835" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4836">
+      <c r="A4836" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:58</t>
+        </is>
+      </c>
+      <c r="B4836" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4836" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4837">
+      <c r="A4837" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:36:59</t>
+        </is>
+      </c>
+      <c r="B4837" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4837" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4838">
+      <c r="A4838" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:05</t>
+        </is>
+      </c>
+      <c r="B4838" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4838" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4839">
+      <c r="A4839" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:06</t>
+        </is>
+      </c>
+      <c r="B4839" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4839" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4840">
+      <c r="A4840" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:13</t>
+        </is>
+      </c>
+      <c r="B4840" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4840" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4841">
+      <c r="A4841" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:14</t>
+        </is>
+      </c>
+      <c r="B4841" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4841" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4842">
+      <c r="A4842" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:20</t>
+        </is>
+      </c>
+      <c r="B4842" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4842" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4843">
+      <c r="A4843" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:21</t>
+        </is>
+      </c>
+      <c r="B4843" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4843" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4844">
+      <c r="A4844" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:27</t>
+        </is>
+      </c>
+      <c r="B4844" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4844" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4845">
+      <c r="A4845" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:28</t>
+        </is>
+      </c>
+      <c r="B4845" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4845" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4846">
+      <c r="A4846" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:35</t>
+        </is>
+      </c>
+      <c r="B4846" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4846" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4847">
+      <c r="A4847" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:36</t>
+        </is>
+      </c>
+      <c r="B4847" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4847" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4848">
+      <c r="A4848" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:42</t>
+        </is>
+      </c>
+      <c r="B4848" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4848" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4849">
+      <c r="A4849" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:43</t>
+        </is>
+      </c>
+      <c r="B4849" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4849" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4850">
+      <c r="A4850" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:49</t>
+        </is>
+      </c>
+      <c r="B4850" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4850" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4851">
+      <c r="A4851" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:50</t>
+        </is>
+      </c>
+      <c r="B4851" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4851" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4852">
+      <c r="A4852" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:56</t>
+        </is>
+      </c>
+      <c r="B4852" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4852" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4853">
+      <c r="A4853" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:37:58</t>
+        </is>
+      </c>
+      <c r="B4853" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4853" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4854">
+      <c r="A4854" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:04</t>
+        </is>
+      </c>
+      <c r="B4854" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4854" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4855">
+      <c r="A4855" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:05</t>
+        </is>
+      </c>
+      <c r="B4855" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4855" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4856">
+      <c r="A4856" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:11</t>
+        </is>
+      </c>
+      <c r="B4856" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4856" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4857">
+      <c r="A4857" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:12</t>
+        </is>
+      </c>
+      <c r="B4857" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4857" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4858">
+      <c r="A4858" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:18</t>
+        </is>
+      </c>
+      <c r="B4858" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4858" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4859">
+      <c r="A4859" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:20</t>
+        </is>
+      </c>
+      <c r="B4859" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4859" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4860">
+      <c r="A4860" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:26</t>
+        </is>
+      </c>
+      <c r="B4860" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4860" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4861">
+      <c r="A4861" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:27</t>
+        </is>
+      </c>
+      <c r="B4861" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4861" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4862">
+      <c r="A4862" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:33</t>
+        </is>
+      </c>
+      <c r="B4862" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4862" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4863">
+      <c r="A4863" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:34</t>
+        </is>
+      </c>
+      <c r="B4863" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4863" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4864">
+      <c r="A4864" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:40</t>
+        </is>
+      </c>
+      <c r="B4864" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4864" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4865">
+      <c r="A4865" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:41</t>
+        </is>
+      </c>
+      <c r="B4865" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4865" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4866">
+      <c r="A4866" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:48</t>
+        </is>
+      </c>
+      <c r="B4866" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4866" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4867">
+      <c r="A4867" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:49</t>
+        </is>
+      </c>
+      <c r="B4867" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4867" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4868">
+      <c r="A4868" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:55</t>
+        </is>
+      </c>
+      <c r="B4868" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4868" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4869">
+      <c r="A4869" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:38:56</t>
+        </is>
+      </c>
+      <c r="B4869" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4869" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4870">
+      <c r="A4870" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:02</t>
+        </is>
+      </c>
+      <c r="B4870" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4870" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4871">
+      <c r="A4871" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:04</t>
+        </is>
+      </c>
+      <c r="B4871" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4871" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4872">
+      <c r="A4872" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:10</t>
+        </is>
+      </c>
+      <c r="B4872" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4872" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:11</t>
+        </is>
+      </c>
+      <c r="B4873" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4873" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4874">
+      <c r="A4874" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:17</t>
+        </is>
+      </c>
+      <c r="B4874" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4874" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:18</t>
+        </is>
+      </c>
+      <c r="B4875" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4875" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4876">
+      <c r="A4876" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:24</t>
+        </is>
+      </c>
+      <c r="B4876" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4876" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:25</t>
+        </is>
+      </c>
+      <c r="B4877" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4877" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4878">
+      <c r="A4878" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:31</t>
+        </is>
+      </c>
+      <c r="B4878" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4878" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4879">
+      <c r="A4879" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:32</t>
+        </is>
+      </c>
+      <c r="B4879" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4879" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4880">
+      <c r="A4880" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:39</t>
+        </is>
+      </c>
+      <c r="B4880" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4880" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:40</t>
+        </is>
+      </c>
+      <c r="B4881" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4881" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4882">
+      <c r="A4882" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:46</t>
+        </is>
+      </c>
+      <c r="B4882" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4882" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:47</t>
+        </is>
+      </c>
+      <c r="B4883" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4883" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4884">
+      <c r="A4884" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:53</t>
+        </is>
+      </c>
+      <c r="B4884" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4884" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:39:54</t>
+        </is>
+      </c>
+      <c r="B4885" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4885" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4886">
+      <c r="A4886" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:40:00</t>
+        </is>
+      </c>
+      <c r="B4886" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4886" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:40:02</t>
+        </is>
+      </c>
+      <c r="B4887" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4887" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4888">
+      <c r="A4888" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:40:09</t>
+        </is>
+      </c>
+      <c r="B4888" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4888" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:40:10</t>
+        </is>
+      </c>
+      <c r="B4889" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4889" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4890">
+      <c r="A4890" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:28</t>
+        </is>
+      </c>
+      <c r="B4890" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4890" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:29</t>
+        </is>
+      </c>
+      <c r="B4891" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4891" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4892">
+      <c r="A4892" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:31</t>
+        </is>
+      </c>
+      <c r="B4892" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4892" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:37</t>
+        </is>
+      </c>
+      <c r="B4893" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4893" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4894">
+      <c r="A4894" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:38</t>
+        </is>
+      </c>
+      <c r="B4894" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4894" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:44</t>
+        </is>
+      </c>
+      <c r="B4895" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4895" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4896">
+      <c r="A4896" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:46</t>
+        </is>
+      </c>
+      <c r="B4896" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4896" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:52</t>
+        </is>
+      </c>
+      <c r="B4897" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4897" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4898">
+      <c r="A4898" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:53</t>
+        </is>
+      </c>
+      <c r="B4898" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4898" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4899">
+      <c r="A4899" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:41:59</t>
+        </is>
+      </c>
+      <c r="B4899" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4899" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4900">
+      <c r="A4900" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:42:00</t>
+        </is>
+      </c>
+      <c r="B4900" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4900" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4901">
+      <c r="A4901" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:42:07</t>
+        </is>
+      </c>
+      <c r="B4901" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4901" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4902">
+      <c r="A4902" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:42:08</t>
+        </is>
+      </c>
+      <c r="B4902" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4902" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4903">
+      <c r="A4903" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:42:14</t>
+        </is>
+      </c>
+      <c r="B4903" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4903" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4904">
+      <c r="A4904" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:42:15</t>
+        </is>
+      </c>
+      <c r="B4904" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4904" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4905">
+      <c r="A4905" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:43:57</t>
+        </is>
+      </c>
+      <c r="B4905" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4905" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="4906">
+      <c r="A4906" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:43:58</t>
+        </is>
+      </c>
+      <c r="B4906" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4906" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5
+Traceback (most recent call last):
+  File "C:\Users\Administrator\Documents\GitHub\goldiebot-backend\trade_manager.py", line 28, in __enter__
+    raise ConnectionError("Failed to initialize MT5")
+ConnectionError: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4907">
+      <c r="A4907" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:44:00</t>
+        </is>
+      </c>
+      <c r="B4907" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4907" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4908">
+      <c r="A4908" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:44:01</t>
+        </is>
+      </c>
+      <c r="B4908" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4908" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4909">
+      <c r="A4909" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:45:50</t>
+        </is>
+      </c>
+      <c r="B4909" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4909" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4910">
+      <c r="A4910" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:45:51</t>
+        </is>
+      </c>
+      <c r="B4910" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4910" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4911">
+      <c r="A4911" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:45:53</t>
+        </is>
+      </c>
+      <c r="B4911" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4911" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4912">
+      <c r="A4912" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:45:59</t>
+        </is>
+      </c>
+      <c r="B4912" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4912" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:46:00</t>
+        </is>
+      </c>
+      <c r="B4913" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4913" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4914">
+      <c r="A4914" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:46:07</t>
+        </is>
+      </c>
+      <c r="B4914" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4914" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:46:08</t>
+        </is>
+      </c>
+      <c r="B4915" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4915" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4916">
+      <c r="A4916" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:47:55</t>
+        </is>
+      </c>
+      <c r="B4916" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4916" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:47:56</t>
+        </is>
+      </c>
+      <c r="B4917" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4917" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4918">
+      <c r="A4918" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:47:57</t>
+        </is>
+      </c>
+      <c r="B4918" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4918" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:03</t>
+        </is>
+      </c>
+      <c r="B4919" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4919" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4920">
+      <c r="A4920" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:04</t>
+        </is>
+      </c>
+      <c r="B4920" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4920" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:11</t>
+        </is>
+      </c>
+      <c r="B4921" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4921" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4922">
+      <c r="A4922" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:12</t>
+        </is>
+      </c>
+      <c r="B4922" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4922" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4923">
+      <c r="A4923" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:18</t>
+        </is>
+      </c>
+      <c r="B4923" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4923" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4924">
+      <c r="A4924" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:20</t>
+        </is>
+      </c>
+      <c r="B4924" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4924" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4925">
+      <c r="A4925" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:26</t>
+        </is>
+      </c>
+      <c r="B4925" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4925" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4926">
+      <c r="A4926" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:28</t>
+        </is>
+      </c>
+      <c r="B4926" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4926" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4927">
+      <c r="A4927" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:34</t>
+        </is>
+      </c>
+      <c r="B4927" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4927" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4928">
+      <c r="A4928" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:35</t>
+        </is>
+      </c>
+      <c r="B4928" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4928" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4929">
+      <c r="A4929" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:41</t>
+        </is>
+      </c>
+      <c r="B4929" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4929" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4930">
+      <c r="A4930" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:43</t>
+        </is>
+      </c>
+      <c r="B4930" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4930" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4931">
+      <c r="A4931" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:49</t>
+        </is>
+      </c>
+      <c r="B4931" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4931" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4932">
+      <c r="A4932" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:50</t>
+        </is>
+      </c>
+      <c r="B4932" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4932" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4933">
+      <c r="A4933" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:56</t>
+        </is>
+      </c>
+      <c r="B4933" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4933" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4934">
+      <c r="A4934" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:48:58</t>
+        </is>
+      </c>
+      <c r="B4934" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4934" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4935">
+      <c r="A4935" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:04</t>
+        </is>
+      </c>
+      <c r="B4935" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4935" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4936">
+      <c r="A4936" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:05</t>
+        </is>
+      </c>
+      <c r="B4936" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4936" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4937">
+      <c r="A4937" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:12</t>
+        </is>
+      </c>
+      <c r="B4937" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4937" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4938">
+      <c r="A4938" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:13</t>
+        </is>
+      </c>
+      <c r="B4938" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4938" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4939">
+      <c r="A4939" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:14</t>
+        </is>
+      </c>
+      <c r="B4939" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4939" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4940">
+      <c r="A4940" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:20</t>
+        </is>
+      </c>
+      <c r="B4940" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4940" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4941">
+      <c r="A4941" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:21</t>
+        </is>
+      </c>
+      <c r="B4941" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4941" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4942">
+      <c r="A4942" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:27</t>
+        </is>
+      </c>
+      <c r="B4942" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4942" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4943">
+      <c r="A4943" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:29</t>
+        </is>
+      </c>
+      <c r="B4943" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4943" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4944">
+      <c r="A4944" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:35</t>
+        </is>
+      </c>
+      <c r="B4944" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4944" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4945">
+      <c r="A4945" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:36</t>
+        </is>
+      </c>
+      <c r="B4945" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4945" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4946">
+      <c r="A4946" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:42</t>
+        </is>
+      </c>
+      <c r="B4946" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4946" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4947">
+      <c r="A4947" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:43</t>
+        </is>
+      </c>
+      <c r="B4947" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4947" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4948">
+      <c r="A4948" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:49</t>
+        </is>
+      </c>
+      <c r="B4948" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4948" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4949">
+      <c r="A4949" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:50</t>
+        </is>
+      </c>
+      <c r="B4949" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4949" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4950">
+      <c r="A4950" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:56</t>
+        </is>
+      </c>
+      <c r="B4950" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4950" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4951">
+      <c r="A4951" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:49:57</t>
+        </is>
+      </c>
+      <c r="B4951" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4951" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4952">
+      <c r="A4952" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:04</t>
+        </is>
+      </c>
+      <c r="B4952" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4952" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4953">
+      <c r="A4953" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:05</t>
+        </is>
+      </c>
+      <c r="B4953" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4953" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4954">
+      <c r="A4954" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:11</t>
+        </is>
+      </c>
+      <c r="B4954" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4954" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4955">
+      <c r="A4955" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:12</t>
+        </is>
+      </c>
+      <c r="B4955" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4955" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4956">
+      <c r="A4956" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:18</t>
+        </is>
+      </c>
+      <c r="B4956" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4956" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4957">
+      <c r="A4957" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:19</t>
+        </is>
+      </c>
+      <c r="B4957" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4957" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4958">
+      <c r="A4958" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:25</t>
+        </is>
+      </c>
+      <c r="B4958" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4958" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4959">
+      <c r="A4959" t="inlineStr">
+        <is>
+          <t>2025-09-11 14:50:27</t>
+        </is>
+      </c>
+      <c r="B4959" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4959" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection may have been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4960">
+      <c r="A4960" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:01:59</t>
+        </is>
+      </c>
+      <c r="B4960" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4960" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4961">
+      <c r="A4961" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:00</t>
+        </is>
+      </c>
+      <c r="B4961" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4961" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4962">
+      <c r="A4962" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:06</t>
+        </is>
+      </c>
+      <c r="B4962" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4962" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4963">
+      <c r="A4963" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:07</t>
+        </is>
+      </c>
+      <c r="B4963" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4963" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4964">
+      <c r="A4964" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:13</t>
+        </is>
+      </c>
+      <c r="B4964" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4964" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4965">
+      <c r="A4965" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:15</t>
+        </is>
+      </c>
+      <c r="B4965" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4965" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4966">
+      <c r="A4966" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:21</t>
+        </is>
+      </c>
+      <c r="B4966" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4966" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4967">
+      <c r="A4967" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:22</t>
+        </is>
+      </c>
+      <c r="B4967" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4967" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4968">
+      <c r="A4968" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:28</t>
+        </is>
+      </c>
+      <c r="B4968" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4968" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4969">
+      <c r="A4969" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:30</t>
+        </is>
+      </c>
+      <c r="B4969" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4969" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4970">
+      <c r="A4970" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:36</t>
+        </is>
+      </c>
+      <c r="B4970" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4970" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4971">
+      <c r="A4971" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:37</t>
+        </is>
+      </c>
+      <c r="B4971" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4971" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4972">
+      <c r="A4972" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:43</t>
+        </is>
+      </c>
+      <c r="B4972" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4972" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4973">
+      <c r="A4973" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:45</t>
+        </is>
+      </c>
+      <c r="B4973" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4973" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4974">
+      <c r="A4974" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:46</t>
+        </is>
+      </c>
+      <c r="B4974" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4974" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4975">
+      <c r="A4975" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:02:47</t>
+        </is>
+      </c>
+      <c r="B4975" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4975" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4976">
+      <c r="A4976" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:05</t>
+        </is>
+      </c>
+      <c r="B4976" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4976" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4977">
+      <c r="A4977" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:06</t>
+        </is>
+      </c>
+      <c r="B4977" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4977" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4978">
+      <c r="A4978" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:13</t>
+        </is>
+      </c>
+      <c r="B4978" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4978" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4979">
+      <c r="A4979" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:14</t>
+        </is>
+      </c>
+      <c r="B4979" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4979" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4980">
+      <c r="A4980" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:20</t>
+        </is>
+      </c>
+      <c r="B4980" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4980" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4981">
+      <c r="A4981" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:21</t>
+        </is>
+      </c>
+      <c r="B4981" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4981" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4982">
+      <c r="A4982" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:27</t>
+        </is>
+      </c>
+      <c r="B4982" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4982" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4983">
+      <c r="A4983" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:29</t>
+        </is>
+      </c>
+      <c r="B4983" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4983" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4984">
+      <c r="A4984" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:35</t>
+        </is>
+      </c>
+      <c r="B4984" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4984" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4985">
+      <c r="A4985" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:36</t>
+        </is>
+      </c>
+      <c r="B4985" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4985" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4986">
+      <c r="A4986" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:42</t>
+        </is>
+      </c>
+      <c r="B4986" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4986" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4987">
+      <c r="A4987" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:43</t>
+        </is>
+      </c>
+      <c r="B4987" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4987" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4988">
+      <c r="A4988" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:50</t>
+        </is>
+      </c>
+      <c r="B4988" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4988" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4989">
+      <c r="A4989" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:51</t>
+        </is>
+      </c>
+      <c r="B4989" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4989" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4990">
+      <c r="A4990" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:52</t>
+        </is>
+      </c>
+      <c r="B4990" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C4990" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4991">
+      <c r="A4991" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:03:53</t>
+        </is>
+      </c>
+      <c r="B4991" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4991" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="4992">
+      <c r="A4992" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:12</t>
+        </is>
+      </c>
+      <c r="B4992" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4992" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4993">
+      <c r="A4993" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:13</t>
+        </is>
+      </c>
+      <c r="B4993" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4993" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4994">
+      <c r="A4994" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:19</t>
+        </is>
+      </c>
+      <c r="B4994" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4994" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4995">
+      <c r="A4995" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:20</t>
+        </is>
+      </c>
+      <c r="B4995" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4995" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4996">
+      <c r="A4996" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:26</t>
+        </is>
+      </c>
+      <c r="B4996" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4996" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4997">
+      <c r="A4997" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:27</t>
+        </is>
+      </c>
+      <c r="B4997" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4997" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4998">
+      <c r="A4998" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:33</t>
+        </is>
+      </c>
+      <c r="B4998" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4998" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4999">
+      <c r="A4999" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:34</t>
+        </is>
+      </c>
+      <c r="B4999" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C4999" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5000">
+      <c r="A5000" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:41</t>
+        </is>
+      </c>
+      <c r="B5000" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5000" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5001">
+      <c r="A5001" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:42</t>
+        </is>
+      </c>
+      <c r="B5001" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5001" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5002">
+      <c r="A5002" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:48</t>
+        </is>
+      </c>
+      <c r="B5002" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5002" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5003">
+      <c r="A5003" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:49</t>
+        </is>
+      </c>
+      <c r="B5003" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5003" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5004">
+      <c r="A5004" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:55</t>
+        </is>
+      </c>
+      <c r="B5004" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5004" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5005">
+      <c r="A5005" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:56</t>
+        </is>
+      </c>
+      <c r="B5005" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5005" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5006">
+      <c r="A5006" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:57</t>
+        </is>
+      </c>
+      <c r="B5006" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5006" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5007">
+      <c r="A5007" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:04:58</t>
+        </is>
+      </c>
+      <c r="B5007" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5007" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5008">
+      <c r="A5008" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:16</t>
+        </is>
+      </c>
+      <c r="B5008" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5008" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5009">
+      <c r="A5009" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:18</t>
+        </is>
+      </c>
+      <c r="B5009" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5009" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5010">
+      <c r="A5010" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:24</t>
+        </is>
+      </c>
+      <c r="B5010" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5010" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5011">
+      <c r="A5011" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:25</t>
+        </is>
+      </c>
+      <c r="B5011" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5011" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5012">
+      <c r="A5012" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:31</t>
+        </is>
+      </c>
+      <c r="B5012" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5012" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5013">
+      <c r="A5013" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:32</t>
+        </is>
+      </c>
+      <c r="B5013" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5013" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5014">
+      <c r="A5014" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:38</t>
+        </is>
+      </c>
+      <c r="B5014" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5014" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5015">
+      <c r="A5015" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:39</t>
+        </is>
+      </c>
+      <c r="B5015" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5015" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:45</t>
+        </is>
+      </c>
+      <c r="B5016" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5016" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:47</t>
+        </is>
+      </c>
+      <c r="B5017" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5017" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5018">
+      <c r="A5018" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:53</t>
+        </is>
+      </c>
+      <c r="B5018" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5018" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5019">
+      <c r="A5019" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:05:54</t>
+        </is>
+      </c>
+      <c r="B5019" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5019" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5020">
+      <c r="A5020" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:00</t>
+        </is>
+      </c>
+      <c r="B5020" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5020" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5021">
+      <c r="A5021" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:01</t>
+        </is>
+      </c>
+      <c r="B5021" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5021" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5022">
+      <c r="A5022" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:03</t>
+        </is>
+      </c>
+      <c r="B5022" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5022" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5023">
+      <c r="A5023" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:04</t>
+        </is>
+      </c>
+      <c r="B5023" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5023" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5024">
+      <c r="A5024" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:22</t>
+        </is>
+      </c>
+      <c r="B5024" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5024" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5025">
+      <c r="A5025" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:23</t>
+        </is>
+      </c>
+      <c r="B5025" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5025" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5026">
+      <c r="A5026" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:30</t>
+        </is>
+      </c>
+      <c r="B5026" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5026" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5027">
+      <c r="A5027" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:31</t>
+        </is>
+      </c>
+      <c r="B5027" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5027" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5028">
+      <c r="A5028" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:37</t>
+        </is>
+      </c>
+      <c r="B5028" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5028" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5029">
+      <c r="A5029" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:38</t>
+        </is>
+      </c>
+      <c r="B5029" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5029" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5030">
+      <c r="A5030" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:44</t>
+        </is>
+      </c>
+      <c r="B5030" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5030" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5031">
+      <c r="A5031" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:06:46</t>
+        </is>
+      </c>
+      <c r="B5031" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5031" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5032">
+      <c r="A5032" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:08:39</t>
+        </is>
+      </c>
+      <c r="B5032" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5032" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5033">
+      <c r="A5033" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:08:40</t>
+        </is>
+      </c>
+      <c r="B5033" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5033" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5034">
+      <c r="A5034" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:08:42</t>
+        </is>
+      </c>
+      <c r="B5034" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5034" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5035">
+      <c r="A5035" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:08:43</t>
+        </is>
+      </c>
+      <c r="B5035" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5035" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5036">
+      <c r="A5036" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:01</t>
+        </is>
+      </c>
+      <c r="B5036" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5036" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5037">
+      <c r="A5037" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:03</t>
+        </is>
+      </c>
+      <c r="B5037" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5037" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5038">
+      <c r="A5038" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:09</t>
+        </is>
+      </c>
+      <c r="B5038" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5038" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5039">
+      <c r="A5039" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:11</t>
+        </is>
+      </c>
+      <c r="B5039" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5039" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5040">
+      <c r="A5040" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:17</t>
+        </is>
+      </c>
+      <c r="B5040" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5040" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5041">
+      <c r="A5041" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:18</t>
+        </is>
+      </c>
+      <c r="B5041" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5041" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5042">
+      <c r="A5042" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:24</t>
+        </is>
+      </c>
+      <c r="B5042" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5042" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5043">
+      <c r="A5043" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:25</t>
+        </is>
+      </c>
+      <c r="B5043" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5043" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5044">
+      <c r="A5044" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:31</t>
+        </is>
+      </c>
+      <c r="B5044" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5044" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5045">
+      <c r="A5045" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:33</t>
+        </is>
+      </c>
+      <c r="B5045" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5045" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5046">
+      <c r="A5046" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:39</t>
+        </is>
+      </c>
+      <c r="B5046" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5046" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5047">
+      <c r="A5047" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:40</t>
+        </is>
+      </c>
+      <c r="B5047" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5047" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5048">
+      <c r="A5048" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:46</t>
+        </is>
+      </c>
+      <c r="B5048" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5048" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5049">
+      <c r="A5049" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:47</t>
+        </is>
+      </c>
+      <c r="B5049" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5049" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5050">
+      <c r="A5050" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:48</t>
+        </is>
+      </c>
+      <c r="B5050" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5050" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5051">
+      <c r="A5051" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:50</t>
+        </is>
+      </c>
+      <c r="B5051" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5051" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5052">
+      <c r="A5052" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:09:59</t>
+        </is>
+      </c>
+      <c r="B5052" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5052" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5053">
+      <c r="A5053" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:01</t>
+        </is>
+      </c>
+      <c r="B5053" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5053" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5054">
+      <c r="A5054" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:03</t>
+        </is>
+      </c>
+      <c r="B5054" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5054" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5055">
+      <c r="A5055" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:05</t>
+        </is>
+      </c>
+      <c r="B5055" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5055" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5056">
+      <c r="A5056" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:23</t>
+        </is>
+      </c>
+      <c r="B5056" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5056" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5057">
+      <c r="A5057" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:24</t>
+        </is>
+      </c>
+      <c r="B5057" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5057" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5058">
+      <c r="A5058" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:30</t>
+        </is>
+      </c>
+      <c r="B5058" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5058" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5059">
+      <c r="A5059" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:32</t>
+        </is>
+      </c>
+      <c r="B5059" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5059" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5060">
+      <c r="A5060" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:38</t>
+        </is>
+      </c>
+      <c r="B5060" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5060" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5061">
+      <c r="A5061" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:10:39</t>
+        </is>
+      </c>
+      <c r="B5061" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5061" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5062">
+      <c r="A5062" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:35</t>
+        </is>
+      </c>
+      <c r="B5062" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5062" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:37</t>
+        </is>
+      </c>
+      <c r="B5063" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5063" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5064">
+      <c r="A5064" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:39</t>
+        </is>
+      </c>
+      <c r="B5064" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5064" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:40</t>
+        </is>
+      </c>
+      <c r="B5065" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5065" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:58</t>
+        </is>
+      </c>
+      <c r="B5066" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5066" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:13:59</t>
+        </is>
+      </c>
+      <c r="B5067" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5067" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5068">
+      <c r="A5068" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:06</t>
+        </is>
+      </c>
+      <c r="B5068" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5068" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:07</t>
+        </is>
+      </c>
+      <c r="B5069" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5069" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:13</t>
+        </is>
+      </c>
+      <c r="B5070" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5070" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:14</t>
+        </is>
+      </c>
+      <c r="B5071" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5071" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:20</t>
+        </is>
+      </c>
+      <c r="B5072" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5072" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5073">
+      <c r="A5073" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:22</t>
+        </is>
+      </c>
+      <c r="B5073" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5073" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:28</t>
+        </is>
+      </c>
+      <c r="B5074" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5074" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5075">
+      <c r="A5075" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:29</t>
+        </is>
+      </c>
+      <c r="B5075" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5075" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5076">
+      <c r="A5076" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:35</t>
+        </is>
+      </c>
+      <c r="B5076" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5076" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5077">
+      <c r="A5077" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:37</t>
+        </is>
+      </c>
+      <c r="B5077" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5077" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5078">
+      <c r="A5078" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:43</t>
+        </is>
+      </c>
+      <c r="B5078" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5078" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5079">
+      <c r="A5079" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:44</t>
+        </is>
+      </c>
+      <c r="B5079" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5079" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5080">
+      <c r="A5080" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:45</t>
+        </is>
+      </c>
+      <c r="B5080" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5080" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:14:47</t>
+        </is>
+      </c>
+      <c r="B5081" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5081" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:05</t>
+        </is>
+      </c>
+      <c r="B5082" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5082" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:06</t>
+        </is>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5083" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:12</t>
+        </is>
+      </c>
+      <c r="B5084" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5084" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:13</t>
+        </is>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5085" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:20</t>
+        </is>
+      </c>
+      <c r="B5086" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5086" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:21</t>
+        </is>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5087" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:27</t>
+        </is>
+      </c>
+      <c r="B5088" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5088" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:28</t>
+        </is>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5089" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:34</t>
+        </is>
+      </c>
+      <c r="B5090" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5090" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5091">
+      <c r="A5091" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:35</t>
+        </is>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5091" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:41</t>
+        </is>
+      </c>
+      <c r="B5092" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5092" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:42</t>
+        </is>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5093" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:48</t>
+        </is>
+      </c>
+      <c r="B5094" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5094" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:50</t>
+        </is>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5095" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:51</t>
+        </is>
+      </c>
+      <c r="B5096" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5096" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:15:52</t>
+        </is>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5097" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:10</t>
+        </is>
+      </c>
+      <c r="B5098" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5098" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:11</t>
+        </is>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5099" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5100">
+      <c r="A5100" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:17</t>
+        </is>
+      </c>
+      <c r="B5100" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5100" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5101">
+      <c r="A5101" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:18</t>
+        </is>
+      </c>
+      <c r="B5101" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5101" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5102">
+      <c r="A5102" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:24</t>
+        </is>
+      </c>
+      <c r="B5102" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5102" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5103">
+      <c r="A5103" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:25</t>
+        </is>
+      </c>
+      <c r="B5103" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5103" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5104">
+      <c r="A5104" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:31</t>
+        </is>
+      </c>
+      <c r="B5104" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5104" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5105">
+      <c r="A5105" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:32</t>
+        </is>
+      </c>
+      <c r="B5105" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5105" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5106">
+      <c r="A5106" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:38</t>
+        </is>
+      </c>
+      <c r="B5106" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5106" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5107">
+      <c r="A5107" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:39</t>
+        </is>
+      </c>
+      <c r="B5107" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5107" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5108">
+      <c r="A5108" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:46</t>
+        </is>
+      </c>
+      <c r="B5108" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5108" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5109">
+      <c r="A5109" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:47</t>
+        </is>
+      </c>
+      <c r="B5109" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5109" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5110">
+      <c r="A5110" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:53</t>
+        </is>
+      </c>
+      <c r="B5110" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5110" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5111">
+      <c r="A5111" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:54</t>
+        </is>
+      </c>
+      <c r="B5111" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5111" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5112">
+      <c r="A5112" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:55</t>
+        </is>
+      </c>
+      <c r="B5112" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5112" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5113">
+      <c r="A5113" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:16:56</t>
+        </is>
+      </c>
+      <c r="B5113" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5113" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5114">
+      <c r="A5114" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:14</t>
+        </is>
+      </c>
+      <c r="B5114" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5114" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5115">
+      <c r="A5115" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:15</t>
+        </is>
+      </c>
+      <c r="B5115" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5115" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5116">
+      <c r="A5116" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:22</t>
+        </is>
+      </c>
+      <c r="B5116" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5116" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5117">
+      <c r="A5117" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:23</t>
+        </is>
+      </c>
+      <c r="B5117" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5117" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5118">
+      <c r="A5118" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:30</t>
+        </is>
+      </c>
+      <c r="B5118" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5118" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5119">
+      <c r="A5119" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:31</t>
+        </is>
+      </c>
+      <c r="B5119" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5119" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5120">
+      <c r="A5120" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:37</t>
+        </is>
+      </c>
+      <c r="B5120" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5120" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5121">
+      <c r="A5121" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:38</t>
+        </is>
+      </c>
+      <c r="B5121" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5121" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5122">
+      <c r="A5122" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:44</t>
+        </is>
+      </c>
+      <c r="B5122" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5122" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5123">
+      <c r="A5123" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:45</t>
+        </is>
+      </c>
+      <c r="B5123" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5123" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5124">
+      <c r="A5124" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:51</t>
+        </is>
+      </c>
+      <c r="B5124" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5124" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5125">
+      <c r="A5125" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:52</t>
+        </is>
+      </c>
+      <c r="B5125" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5125" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5126">
+      <c r="A5126" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:17:59</t>
+        </is>
+      </c>
+      <c r="B5126" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5126" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5127">
+      <c r="A5127" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:00</t>
+        </is>
+      </c>
+      <c r="B5127" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5127" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5128">
+      <c r="A5128" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:01</t>
+        </is>
+      </c>
+      <c r="B5128" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5128" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5129">
+      <c r="A5129" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:02</t>
+        </is>
+      </c>
+      <c r="B5129" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5129" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5130">
+      <c r="A5130" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:20</t>
+        </is>
+      </c>
+      <c r="B5130" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5130" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5131">
+      <c r="A5131" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:21</t>
+        </is>
+      </c>
+      <c r="B5131" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5131" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5132">
+      <c r="A5132" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:27</t>
+        </is>
+      </c>
+      <c r="B5132" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5132" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5133">
+      <c r="A5133" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:28</t>
+        </is>
+      </c>
+      <c r="B5133" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5133" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5134">
+      <c r="A5134" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:34</t>
+        </is>
+      </c>
+      <c r="B5134" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5134" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5135">
+      <c r="A5135" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:35</t>
+        </is>
+      </c>
+      <c r="B5135" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5135" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5136">
+      <c r="A5136" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:42</t>
+        </is>
+      </c>
+      <c r="B5136" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5136" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5137">
+      <c r="A5137" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:43</t>
+        </is>
+      </c>
+      <c r="B5137" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5137" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5138">
+      <c r="A5138" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:49</t>
+        </is>
+      </c>
+      <c r="B5138" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5138" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5139">
+      <c r="A5139" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:50</t>
+        </is>
+      </c>
+      <c r="B5139" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5139" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5140">
+      <c r="A5140" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:56</t>
+        </is>
+      </c>
+      <c r="B5140" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5140" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5141">
+      <c r="A5141" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:18:57</t>
+        </is>
+      </c>
+      <c r="B5141" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5141" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5142">
+      <c r="A5142" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:03</t>
+        </is>
+      </c>
+      <c r="B5142" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5142" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5143">
+      <c r="A5143" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:04</t>
+        </is>
+      </c>
+      <c r="B5143" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5143" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5144">
+      <c r="A5144" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:05</t>
+        </is>
+      </c>
+      <c r="B5144" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5144" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5145">
+      <c r="A5145" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:07</t>
+        </is>
+      </c>
+      <c r="B5145" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5145" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5146">
+      <c r="A5146" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:25</t>
+        </is>
+      </c>
+      <c r="B5146" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5146" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5147">
+      <c r="A5147" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:26</t>
+        </is>
+      </c>
+      <c r="B5147" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5147" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5148">
+      <c r="A5148" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:32</t>
+        </is>
+      </c>
+      <c r="B5148" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5148" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5149">
+      <c r="A5149" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:33</t>
+        </is>
+      </c>
+      <c r="B5149" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5149" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5150">
+      <c r="A5150" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:39</t>
+        </is>
+      </c>
+      <c r="B5150" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5150" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:40</t>
+        </is>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5151" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:47</t>
+        </is>
+      </c>
+      <c r="B5152" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5152" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:48</t>
+        </is>
+      </c>
+      <c r="B5153" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5153" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:54</t>
+        </is>
+      </c>
+      <c r="B5154" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5154" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:19:55</t>
+        </is>
+      </c>
+      <c r="B5155" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5155" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:02</t>
+        </is>
+      </c>
+      <c r="B5156" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5156" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5157">
+      <c r="A5157" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:04</t>
+        </is>
+      </c>
+      <c r="B5157" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5157" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:11</t>
+        </is>
+      </c>
+      <c r="B5158" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5158" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:13</t>
+        </is>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5159" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:14</t>
+        </is>
+      </c>
+      <c r="B5160" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5160" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:15</t>
+        </is>
+      </c>
+      <c r="B5161" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5161" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:34</t>
+        </is>
+      </c>
+      <c r="B5162" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5162" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:35</t>
+        </is>
+      </c>
+      <c r="B5163" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5163" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:41</t>
+        </is>
+      </c>
+      <c r="B5164" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5164" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:42</t>
+        </is>
+      </c>
+      <c r="B5165" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5165" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:48</t>
+        </is>
+      </c>
+      <c r="B5166" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5166" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:49</t>
+        </is>
+      </c>
+      <c r="B5167" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5167" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:56</t>
+        </is>
+      </c>
+      <c r="B5168" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5168" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:20:57</t>
+        </is>
+      </c>
+      <c r="B5169" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5169" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:03</t>
+        </is>
+      </c>
+      <c r="B5170" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5170" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:04</t>
+        </is>
+      </c>
+      <c r="B5171" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5171" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:10</t>
+        </is>
+      </c>
+      <c r="B5172" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5172" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:12</t>
+        </is>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5173" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:18</t>
+        </is>
+      </c>
+      <c r="B5174" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5174" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:19</t>
+        </is>
+      </c>
+      <c r="B5175" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5175" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:20</t>
+        </is>
+      </c>
+      <c r="B5176" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5176" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:21</t>
+        </is>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5177" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:39</t>
+        </is>
+      </c>
+      <c r="B5178" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5178" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:40</t>
+        </is>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5179" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:47</t>
+        </is>
+      </c>
+      <c r="B5180" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5180" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:48</t>
+        </is>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5181" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:54</t>
+        </is>
+      </c>
+      <c r="B5182" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5182" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:21:55</t>
+        </is>
+      </c>
+      <c r="B5183" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5183" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:01</t>
+        </is>
+      </c>
+      <c r="B5184" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5184" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:03</t>
+        </is>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5185" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:09</t>
+        </is>
+      </c>
+      <c r="B5186" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5186" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:10</t>
+        </is>
+      </c>
+      <c r="B5187" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5187" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:16</t>
+        </is>
+      </c>
+      <c r="B5188" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5188" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:17</t>
+        </is>
+      </c>
+      <c r="B5189" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5189" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:24</t>
+        </is>
+      </c>
+      <c r="B5190" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5190" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:25</t>
+        </is>
+      </c>
+      <c r="B5191" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5191" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:26</t>
+        </is>
+      </c>
+      <c r="B5192" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5192" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:27</t>
+        </is>
+      </c>
+      <c r="B5193" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5193" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:45</t>
+        </is>
+      </c>
+      <c r="B5194" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5194" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:47</t>
+        </is>
+      </c>
+      <c r="B5195" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5195" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:53</t>
+        </is>
+      </c>
+      <c r="B5196" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5196" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:22:54</t>
+        </is>
+      </c>
+      <c r="B5197" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5197" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:00</t>
+        </is>
+      </c>
+      <c r="B5198" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5198" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:02</t>
+        </is>
+      </c>
+      <c r="B5199" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5199" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:08</t>
+        </is>
+      </c>
+      <c r="B5200" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5200" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:09</t>
+        </is>
+      </c>
+      <c r="B5201" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5201" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:15</t>
+        </is>
+      </c>
+      <c r="B5202" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5202" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:16</t>
+        </is>
+      </c>
+      <c r="B5203" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5203" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:23</t>
+        </is>
+      </c>
+      <c r="B5204" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5204" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:24</t>
+        </is>
+      </c>
+      <c r="B5205" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5205" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:30</t>
+        </is>
+      </c>
+      <c r="B5206" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5206" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:31</t>
+        </is>
+      </c>
+      <c r="B5207" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5207" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:33</t>
+        </is>
+      </c>
+      <c r="B5208" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5208" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:34</t>
+        </is>
+      </c>
+      <c r="B5209" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5209" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:52</t>
+        </is>
+      </c>
+      <c r="B5210" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5210" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:53</t>
+        </is>
+      </c>
+      <c r="B5211" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5211" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:23:59</t>
+        </is>
+      </c>
+      <c r="B5212" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5212" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:00</t>
+        </is>
+      </c>
+      <c r="B5213" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5213" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:06</t>
+        </is>
+      </c>
+      <c r="B5214" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5214" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:07</t>
+        </is>
+      </c>
+      <c r="B5215" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5215" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:14</t>
+        </is>
+      </c>
+      <c r="B5216" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5216" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:15</t>
+        </is>
+      </c>
+      <c r="B5217" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5217" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:21</t>
+        </is>
+      </c>
+      <c r="B5218" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5218" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:22</t>
+        </is>
+      </c>
+      <c r="B5219" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5219" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:24:29</t>
+        </is>
+      </c>
+      <c r="B5220" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5220" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:03</t>
+        </is>
+      </c>
+      <c r="B5221" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5221" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:05</t>
+        </is>
+      </c>
+      <c r="B5222" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5222" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:07</t>
+        </is>
+      </c>
+      <c r="B5223" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5223" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:08</t>
+        </is>
+      </c>
+      <c r="B5224" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5224" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:26</t>
+        </is>
+      </c>
+      <c r="B5225" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5225" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:27</t>
+        </is>
+      </c>
+      <c r="B5226" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5226" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:34</t>
+        </is>
+      </c>
+      <c r="B5227" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5227" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:35</t>
+        </is>
+      </c>
+      <c r="B5228" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5228" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:41</t>
+        </is>
+      </c>
+      <c r="B5229" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5229" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:42</t>
+        </is>
+      </c>
+      <c r="B5230" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5230" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:49</t>
+        </is>
+      </c>
+      <c r="B5231" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5231" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:50</t>
+        </is>
+      </c>
+      <c r="B5232" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5232" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:56</t>
+        </is>
+      </c>
+      <c r="B5233" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5233" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:25:57</t>
+        </is>
+      </c>
+      <c r="B5234" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5234" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:03</t>
+        </is>
+      </c>
+      <c r="B5235" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5235" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:04</t>
+        </is>
+      </c>
+      <c r="B5236" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5236" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:11</t>
+        </is>
+      </c>
+      <c r="B5237" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5237" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:12</t>
+        </is>
+      </c>
+      <c r="B5238" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5238" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:13</t>
+        </is>
+      </c>
+      <c r="B5239" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5239" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:14</t>
+        </is>
+      </c>
+      <c r="B5240" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5240" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:32</t>
+        </is>
+      </c>
+      <c r="B5241" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5241" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:33</t>
+        </is>
+      </c>
+      <c r="B5242" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5242" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:40</t>
+        </is>
+      </c>
+      <c r="B5243" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5243" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:41</t>
+        </is>
+      </c>
+      <c r="B5244" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5244" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:47</t>
+        </is>
+      </c>
+      <c r="B5245" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5245" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:48</t>
+        </is>
+      </c>
+      <c r="B5246" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5246" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:54</t>
+        </is>
+      </c>
+      <c r="B5247" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5247" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:26:56</t>
+        </is>
+      </c>
+      <c r="B5248" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5248" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:02</t>
+        </is>
+      </c>
+      <c r="B5249" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5249" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:03</t>
+        </is>
+      </c>
+      <c r="B5250" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5250" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:09</t>
+        </is>
+      </c>
+      <c r="B5251" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5251" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:11</t>
+        </is>
+      </c>
+      <c r="B5252" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5252" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:17</t>
+        </is>
+      </c>
+      <c r="B5253" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5253" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:18</t>
+        </is>
+      </c>
+      <c r="B5254" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5254" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:19</t>
+        </is>
+      </c>
+      <c r="B5255" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5255" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:20</t>
+        </is>
+      </c>
+      <c r="B5256" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5256" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:39</t>
+        </is>
+      </c>
+      <c r="B5257" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5257" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:40</t>
+        </is>
+      </c>
+      <c r="B5258" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5258" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:46</t>
+        </is>
+      </c>
+      <c r="B5259" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5259" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:27:47</t>
+        </is>
+      </c>
+      <c r="B5260" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5260" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:10</t>
+        </is>
+      </c>
+      <c r="B5261" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5261" t="inlineStr">
+        <is>
+          <t>MT5 initialize() failed, error code = (-10005, 'IPC timeout')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:12</t>
+        </is>
+      </c>
+      <c r="B5262" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5262" t="inlineStr">
+        <is>
+          <t>An exception occurred during MT5 initialization: Failed to initialize MT5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:14</t>
+        </is>
+      </c>
+      <c r="B5263" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5263" t="inlineStr">
+        <is>
+          <t>Could not establish connection to MetaTrader 5 on startup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:16</t>
+        </is>
+      </c>
+      <c r="B5264" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5264" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:35</t>
+        </is>
+      </c>
+      <c r="B5265" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5265" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:36</t>
+        </is>
+      </c>
+      <c r="B5266" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5266" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:43</t>
+        </is>
+      </c>
+      <c r="B5267" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5267" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:45</t>
+        </is>
+      </c>
+      <c r="B5268" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5268" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:51</t>
+        </is>
+      </c>
+      <c r="B5269" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5269" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:52</t>
+        </is>
+      </c>
+      <c r="B5270" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5270" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:22:59</t>
+        </is>
+      </c>
+      <c r="B5271" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5271" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:41</t>
+        </is>
+      </c>
+      <c r="B5272" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5272" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:42</t>
+        </is>
+      </c>
+      <c r="B5273" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5273" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:49</t>
+        </is>
+      </c>
+      <c r="B5274" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5274" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:50</t>
+        </is>
+      </c>
+      <c r="B5275" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5275" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:57</t>
+        </is>
+      </c>
+      <c r="B5276" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5276" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:25:58</t>
+        </is>
+      </c>
+      <c r="B5277" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5277" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:05</t>
+        </is>
+      </c>
+      <c r="B5278" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5278" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:07</t>
+        </is>
+      </c>
+      <c r="B5279" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5279" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:14</t>
+        </is>
+      </c>
+      <c r="B5280" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5280" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:15</t>
+        </is>
+      </c>
+      <c r="B5281" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5281" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:22</t>
+        </is>
+      </c>
+      <c r="B5282" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5282" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:23</t>
+        </is>
+      </c>
+      <c r="B5283" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5283" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:30</t>
+        </is>
+      </c>
+      <c r="B5284" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5284" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:31</t>
+        </is>
+      </c>
+      <c r="B5285" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5285" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:33</t>
+        </is>
+      </c>
+      <c r="B5286" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5286" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:35</t>
+        </is>
+      </c>
+      <c r="B5287" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5287" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:53</t>
+        </is>
+      </c>
+      <c r="B5288" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5288" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:26:54</t>
+        </is>
+      </c>
+      <c r="B5289" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5289" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:01</t>
+        </is>
+      </c>
+      <c r="B5290" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5290" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:03</t>
+        </is>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5291" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:09</t>
+        </is>
+      </c>
+      <c r="B5292" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5292" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:11</t>
+        </is>
+      </c>
+      <c r="B5293" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5293" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:17</t>
+        </is>
+      </c>
+      <c r="B5294" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5294" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:19</t>
+        </is>
+      </c>
+      <c r="B5295" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5295" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:25</t>
+        </is>
+      </c>
+      <c r="B5296" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5296" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:26</t>
+        </is>
+      </c>
+      <c r="B5297" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5297" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:33</t>
+        </is>
+      </c>
+      <c r="B5298" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5298" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:34</t>
+        </is>
+      </c>
+      <c r="B5299" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5299" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:41</t>
+        </is>
+      </c>
+      <c r="B5300" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5300" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:42</t>
+        </is>
+      </c>
+      <c r="B5301" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5301" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:44</t>
+        </is>
+      </c>
+      <c r="B5302" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5302" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:27:45</t>
+        </is>
+      </c>
+      <c r="B5303" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5303" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:03</t>
+        </is>
+      </c>
+      <c r="B5304" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5304" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:04</t>
+        </is>
+      </c>
+      <c r="B5305" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5305" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:11</t>
+        </is>
+      </c>
+      <c r="B5306" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5306" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:12</t>
+        </is>
+      </c>
+      <c r="B5307" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5307" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:18</t>
+        </is>
+      </c>
+      <c r="B5308" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5308" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:19</t>
+        </is>
+      </c>
+      <c r="B5309" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5309" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:26</t>
+        </is>
+      </c>
+      <c r="B5310" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5310" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:27</t>
+        </is>
+      </c>
+      <c r="B5311" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5311" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:33</t>
+        </is>
+      </c>
+      <c r="B5312" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5312" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:34</t>
+        </is>
+      </c>
+      <c r="B5313" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5313" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:41</t>
+        </is>
+      </c>
+      <c r="B5314" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5314" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:42</t>
+        </is>
+      </c>
+      <c r="B5315" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5315" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:48</t>
+        </is>
+      </c>
+      <c r="B5316" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5316" t="inlineStr">
+        <is>
+          <t>positions_get() returned None. The connection has been lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:50</t>
+        </is>
+      </c>
+      <c r="B5317" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5317" t="inlineStr">
+        <is>
+          <t>Connection to MT5 lost. Retrying... (Attempt 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:53</t>
+        </is>
+      </c>
+      <c r="B5318" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C5318" t="inlineStr">
+        <is>
+          <t>Connection lost for over 30 seconds. Forcing reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="inlineStr">
+        <is>
+          <t>2025-09-11 16:28:56</t>
+        </is>
+      </c>
+      <c r="B5319" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="C5319" t="inlineStr">
+        <is>
+          <t>Main loop exited. Attempting to reconnect in 15 seconds...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
